--- a/docs/AHB_to_APB_Bridge_Verification_Plan.xlsx
+++ b/docs/AHB_to_APB_Bridge_Verification_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Digital Electronics\Grad Proj\Mini Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E45D99-5994-4ED0-8E4F-196159358A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BB377A-9484-4DA9-A518-9FE3472F6CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Verification Plan" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verification Plan'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verification Plan'!$A$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="268">
   <si>
     <t>Feature</t>
   </si>
@@ -692,13 +692,1044 @@
   </si>
   <si>
     <t>cg_apb_response</t>
+  </si>
+  <si>
+    <t>UVM log checking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertions	</t>
+  </si>
+  <si>
+    <t>Handshake: Req rising</t>
+  </si>
+  <si>
+    <t>Handshake: Ack rising</t>
+  </si>
+  <si>
+    <t>Handshake: Req falling</t>
+  </si>
+  <si>
+    <t>Handshake: Ack falling</t>
+  </si>
+  <si>
+    <t>Read data matches APB</t>
+  </si>
+  <si>
+    <t>APBACTIVE during transfer</t>
+  </si>
+  <si>
+    <t>Write data matches AHB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monitor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> across all transfers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Every rising edge of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> happens with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monitor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> across all transfers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Every rising edge of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> happens with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1 (ignored while HRESETn is low).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Every falling edge of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> happens with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1 (ignored while PRESETn is low).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Every falling edge of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> happens with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Req rises only when Ack is low </t>
+  </si>
+  <si>
+    <t>Check Ack rises only when Req is high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Req falls only when Ack is high </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Ack falls only when Req is low </t>
+  </si>
+  <si>
+    <t>Check the AHB read data returned is the data read on APB.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compare </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HRDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with the last </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PRDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when each AHB read completes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At read completion with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HRESP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">=OKAY, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HRDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> equals the last APB read data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Response matches APB</t>
+  </si>
+  <si>
+    <t>Check the AHB response reflects the APB response.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compare </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HRESP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with the last </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSLVERR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when each transfer completes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At transfer completion, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HRESP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> equals </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSLVERR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the last APB transfer.</t>
+    </r>
+  </si>
+  <si>
+    <t>APBACTIVE during handshake</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is raised before the APB transfer starts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monitor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> against the req/ack handshake state.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">=1 whenever </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≠ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_ack_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> stays high while the APB slave is selected.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monitor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> against </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">=1 whenever </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1.</t>
+    </r>
+  </si>
+  <si>
+    <t>Check the data written on APB is the data from the AHB write.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compare </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PWDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with the last accepted AHB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HWDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> during APB writes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">While </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">=1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PWRITE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">=1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PWDATA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> equals the last accepted AHB write data. Reads are not checked.</t>
+    </r>
+  </si>
+  <si>
+    <t>Unmatched request after AHB-only reset</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cover the APB-side branch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>curr_state==fsm_apb_cyc1 &amp; ~s_trans_valid_reg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>nxt_s_ack_p = s_req_p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Run </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ahb_unmatched_req_reset_sequence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mode=RESET_AHB_ONLY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>apb_seq</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> running in the background. Do one transfer, let req/ack settle with the bus idle, pulse HRESETn only, then keep the bus idle and watch the APB side.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The request seen by the APB side carries no valid transfer: PSEL stays low, so no APB transfer and no AHB response. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is high with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PSEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0 for at least 2 PCLK cycles (branch taken). The bridge returns to idle and recovers.</t>
+    </r>
+  </si>
+  <si>
+    <t>Unmatched request after APB reset glitch</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cover the same branch with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_p=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Run the same sequence with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mode=RESET_APB_GLITCH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. After the transfer and settle time, apply a very short PRESETn pulse only (default 1 ns, set by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>apb_glitch_width</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), while </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s_req_h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is still 1. Keep the bus idle and watch the APB side.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Same as the row above: no PSEL or APB transfer, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>APBACTIVE &amp;&amp; !PSEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for at least 2 cycles, bridge returns to idle and recovers.</t>
+    </r>
+  </si>
+  <si>
+    <t>Code coverage (branch/condition)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,6 +1758,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="6">
@@ -800,7 +1836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -822,6 +1858,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1126,8 +2171,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1138,7 +2183,7 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +2209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="26.4">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1188,7 +2233,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="26.4">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1212,7 +2257,7 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="26.4">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1236,7 +2281,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="26.4">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1260,7 +2305,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="26.4">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1284,7 +2329,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="26.4">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1308,7 +2353,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1332,121 +2377,120 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="72">
+      <c r="A9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" ht="72">
+      <c r="A10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="26.4">
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="26.4">
       <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>52</v>
+        <v>221</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="26.4">
       <c r="A13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>58</v>
@@ -1456,45 +2500,45 @@
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
+      <c r="B14" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
@@ -1502,127 +2546,125 @@
       <c r="G15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="26.4">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="26.4">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="26.4">
       <c r="A18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="26.4">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="26.4">
       <c r="A20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>58</v>
@@ -1630,99 +2672,99 @@
       <c r="G20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="H21" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="26.4">
+      <c r="A22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="H22" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="26.4">
+      <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>58</v>
@@ -1730,23 +2772,25 @@
       <c r="G24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>58</v>
@@ -1756,21 +2800,21 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="26.4">
       <c r="A26" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>58</v>
@@ -1778,25 +2822,23 @@
       <c r="G26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>58</v>
@@ -1804,25 +2846,23 @@
       <c r="G27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>58</v>
@@ -1830,161 +2870,171 @@
       <c r="G28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H28" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" ht="26.4">
       <c r="A31" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" ht="26.4">
+      <c r="A34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="26.4">
       <c r="A35" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>140</v>
@@ -1992,23 +3042,25 @@
       <c r="G35" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H35" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="26.4">
       <c r="A36" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>140</v>
@@ -2018,21 +3070,21 @@
       </c>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="26.4">
       <c r="A37" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>140</v>
@@ -2042,21 +3094,21 @@
       </c>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="26.4">
       <c r="A38" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>140</v>
@@ -2066,304 +3118,276 @@
       </c>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="25.2" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" ht="26.4">
+      <c r="A40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="9" customFormat="1" ht="28.8">
+      <c r="A42" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="9" customFormat="1" ht="28.8">
+      <c r="A43" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="9" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="9" customFormat="1" ht="31.2" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="9" customFormat="1" ht="30.6" customHeight="1">
+      <c r="A46" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="30.6" customHeight="1">
+      <c r="A47" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" ht="22.8" customHeight="1">
+      <c r="A48" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" ht="29.4" customHeight="1">
+      <c r="A49" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" ht="26.4">
       <c r="A50" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>168</v>
@@ -2375,21 +3399,21 @@
         <v>164</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="26.4">
       <c r="A51" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>168</v>
@@ -2401,11 +3425,298 @@
         <v>164</v>
       </c>
       <c r="H51" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="26.4">
+      <c r="A52" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="26.4">
+      <c r="A53" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="26.4">
+      <c r="A54" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="26.4">
+      <c r="A55" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="26.4">
+      <c r="A56" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="26.4">
+      <c r="A57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="26.4">
+      <c r="A58" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="26.4">
+      <c r="A59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="39.6">
+      <c r="A60" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="39.6">
+      <c r="A61" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="26.4">
+      <c r="A62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H62" s="5" t="s">
         <v>218</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H47" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>